--- a/wfcv_errors.xlsx
+++ b/wfcv_errors.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -650,7 +650,7 @@
         <v>20216.66666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>33010.08130981971</v>
+        <v>33010.0813098197</v>
       </c>
       <c r="I3" t="n">
         <v>62628.40625</v>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2534.952297138045</v>
+        <v>2534.952297138041</v>
       </c>
       <c r="C4" t="n">
         <v>1846.123697916667</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4903.130554260562</v>
+        <v>4903.130554260567</v>
       </c>
       <c r="C5" t="n">
         <v>1506.654947916667</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4364.963870032749</v>
+        <v>4364.963870032744</v>
       </c>
       <c r="C6" t="n">
         <v>4696.81640625</v>
@@ -905,7 +905,7 @@
         <v>18991.37853657941</v>
       </c>
       <c r="N6" t="n">
-        <v>36046.26910584783</v>
+        <v>36046.26910584789</v>
       </c>
       <c r="O6" t="n">
         <v>64902.41666666666</v>
@@ -923,7 +923,7 @@
         <v>57851.1291583091</v>
       </c>
       <c r="T6" t="n">
-        <v>1865.779971741217</v>
+        <v>1865.779971741221</v>
       </c>
       <c r="U6" t="n">
         <v>1901.279296875</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4241.459117188359</v>
+        <v>4241.459117188363</v>
       </c>
       <c r="C7" t="n">
         <v>3895.307291666667</v>
@@ -984,7 +984,7 @@
         <v>30311.20154526455</v>
       </c>
       <c r="N7" t="n">
-        <v>35751.6972297981</v>
+        <v>35751.69722979813</v>
       </c>
       <c r="O7" t="n">
         <v>44879.83333333334</v>
@@ -1002,7 +1002,7 @@
         <v>82475.4093490758</v>
       </c>
       <c r="T7" t="n">
-        <v>2176.050840488226</v>
+        <v>2176.050840488229</v>
       </c>
       <c r="U7" t="n">
         <v>1603.23046875</v>
@@ -1045,7 +1045,7 @@
         <v>9010.666666666666</v>
       </c>
       <c r="H8" t="n">
-        <v>43006.69727450332</v>
+        <v>43006.69727450333</v>
       </c>
       <c r="I8" t="n">
         <v>38301.96875</v>
@@ -1063,7 +1063,7 @@
         <v>73236.62464174563</v>
       </c>
       <c r="N8" t="n">
-        <v>53527.76611976929</v>
+        <v>53527.76611976931</v>
       </c>
       <c r="O8" t="n">
         <v>53437.63541666666</v>
@@ -1081,7 +1081,7 @@
         <v>131160.5307251292</v>
       </c>
       <c r="T8" t="n">
-        <v>2517.690965668589</v>
+        <v>2517.690965668588</v>
       </c>
       <c r="U8" t="n">
         <v>1749.504557291667</v>
@@ -1142,7 +1142,7 @@
         <v>125159.2796452975</v>
       </c>
       <c r="N9" t="n">
-        <v>68436.70492412256</v>
+        <v>68436.70492412255</v>
       </c>
       <c r="O9" t="n">
         <v>50662.38541666666</v>
@@ -1176,6 +1176,243 @@
       </c>
       <c r="Y9" t="n">
         <v>8703.92228251391</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>12625.28378144078</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8884.592447916666</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14205.41586624551</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10843.15659199261</v>
+      </c>
+      <c r="F10" t="n">
+        <v>209788.1215705172</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13235</v>
+      </c>
+      <c r="H10" t="n">
+        <v>80597.60424170281</v>
+      </c>
+      <c r="I10" t="n">
+        <v>65357.1875</v>
+      </c>
+      <c r="J10" t="n">
+        <v>96433.68371481383</v>
+      </c>
+      <c r="K10" t="n">
+        <v>64840.72240243596</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1421707.365679952</v>
+      </c>
+      <c r="M10" t="n">
+        <v>102523.289456092</v>
+      </c>
+      <c r="N10" t="n">
+        <v>97710.31683253801</v>
+      </c>
+      <c r="O10" t="n">
+        <v>88231.36458333333</v>
+      </c>
+      <c r="P10" t="n">
+        <v>78111.55878251062</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>97369.71417968359</v>
+      </c>
+      <c r="R10" t="n">
+        <v>507482.7967964285</v>
+      </c>
+      <c r="S10" t="n">
+        <v>188461.891614156</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7101.126866522368</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6031.252604166667</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4371.312945010436</v>
+      </c>
+      <c r="W10" t="n">
+        <v>6060.106333717648</v>
+      </c>
+      <c r="X10" t="n">
+        <v>112359.6135028956</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>9804.345708220673</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>16930.15222450698</v>
+      </c>
+      <c r="C11" t="n">
+        <v>20172.94661458333</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17605.31195674774</v>
+      </c>
+      <c r="E11" t="n">
+        <v>15077.79640533145</v>
+      </c>
+      <c r="F11" t="n">
+        <v>461592.454487648</v>
+      </c>
+      <c r="G11" t="n">
+        <v>21409</v>
+      </c>
+      <c r="H11" t="n">
+        <v>104945.0940895262</v>
+      </c>
+      <c r="I11" t="n">
+        <v>88535.5625</v>
+      </c>
+      <c r="J11" t="n">
+        <v>56639.84458176976</v>
+      </c>
+      <c r="K11" t="n">
+        <v>58813.07584177571</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2764385.460942686</v>
+      </c>
+      <c r="M11" t="n">
+        <v>118900.516538205</v>
+      </c>
+      <c r="N11" t="n">
+        <v>149120.9369619409</v>
+      </c>
+      <c r="O11" t="n">
+        <v>115142.3020833333</v>
+      </c>
+      <c r="P11" t="n">
+        <v>80799.97256832389</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>136338.1607174093</v>
+      </c>
+      <c r="R11" t="n">
+        <v>769076.6150977624</v>
+      </c>
+      <c r="S11" t="n">
+        <v>209996.8644067796</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7101.441502044247</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8047.544270833333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2812.466998506448</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4725.741493766734</v>
+      </c>
+      <c r="X11" t="n">
+        <v>261476.9050057846</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>7791.389585307269</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>30045.9692099567</v>
+      </c>
+      <c r="C12" t="n">
+        <v>33288.51302083334</v>
+      </c>
+      <c r="D12" t="n">
+        <v>28684.95923563236</v>
+      </c>
+      <c r="E12" t="n">
+        <v>27201.05017416922</v>
+      </c>
+      <c r="F12" t="n">
+        <v>741193.3133847368</v>
+      </c>
+      <c r="G12" t="n">
+        <v>38913</v>
+      </c>
+      <c r="H12" t="n">
+        <v>166989.5451345228</v>
+      </c>
+      <c r="I12" t="n">
+        <v>127420.0833333333</v>
+      </c>
+      <c r="J12" t="n">
+        <v>98634.54060048012</v>
+      </c>
+      <c r="K12" t="n">
+        <v>106125.3487399855</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3586594.831203761</v>
+      </c>
+      <c r="M12" t="n">
+        <v>239328.7548444103</v>
+      </c>
+      <c r="N12" t="n">
+        <v>198056.0800787407</v>
+      </c>
+      <c r="O12" t="n">
+        <v>165441.53125</v>
+      </c>
+      <c r="P12" t="n">
+        <v>96272.77189015299</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>189378.8568428295</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1670574.647135337</v>
+      </c>
+      <c r="S12" t="n">
+        <v>250038.5833333333</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6799.315943783066</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4225.175130208333</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3671.890866043124</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5721.086488161414</v>
+      </c>
+      <c r="X12" t="n">
+        <v>405487.3094936037</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11306.33083068272</v>
       </c>
     </row>
   </sheetData>
@@ -1189,7 +1426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1423,7 +1660,7 @@
         <v>500240322</v>
       </c>
       <c r="H3" t="n">
-        <v>1575009619.253742</v>
+        <v>1575009619.253741</v>
       </c>
       <c r="I3" t="n">
         <v>5395975399.50944</v>
@@ -1484,7 +1721,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11708603.56973639</v>
+        <v>11708603.56973635</v>
       </c>
       <c r="C4" t="n">
         <v>4318959.679621379</v>
@@ -1502,7 +1739,7 @@
         <v>462569132.6666667</v>
       </c>
       <c r="H4" t="n">
-        <v>2605179779.857343</v>
+        <v>2605179779.857342</v>
       </c>
       <c r="I4" t="n">
         <v>13730454667.92464</v>
@@ -1538,7 +1775,7 @@
         <v>12107428246.84086</v>
       </c>
       <c r="T4" t="n">
-        <v>8796029.302870732</v>
+        <v>8796029.302870721</v>
       </c>
       <c r="U4" t="n">
         <v>9016670.528036753</v>
@@ -1563,7 +1800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39270951.21112776</v>
+        <v>39270951.21112785</v>
       </c>
       <c r="C5" t="n">
         <v>3353391.872889201</v>
@@ -1642,7 +1879,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25748059.16304858</v>
+        <v>25748059.16304857</v>
       </c>
       <c r="C6" t="n">
         <v>33554577.14763895</v>
@@ -1678,7 +1915,7 @@
         <v>545401189.1028966</v>
       </c>
       <c r="N6" t="n">
-        <v>1633025686.547011</v>
+        <v>1633025686.547017</v>
       </c>
       <c r="O6" t="n">
         <v>4336670888.951172</v>
@@ -1696,7 +1933,7 @@
         <v>3670258956.62769</v>
       </c>
       <c r="T6" t="n">
-        <v>3913537.239154214</v>
+        <v>3913537.239154231</v>
       </c>
       <c r="U6" t="n">
         <v>4583518.680309296</v>
@@ -1721,7 +1958,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27974465.49683777</v>
+        <v>27974465.49683785</v>
       </c>
       <c r="C7" t="n">
         <v>17289174.14838664</v>
@@ -1757,7 +1994,7 @@
         <v>1066244815.344419</v>
       </c>
       <c r="N7" t="n">
-        <v>1379537910.312431</v>
+        <v>1379537910.312433</v>
       </c>
       <c r="O7" t="n">
         <v>2658270975.155599</v>
@@ -1775,7 +2012,7 @@
         <v>8503915052.340116</v>
       </c>
       <c r="T7" t="n">
-        <v>5961308.43532187</v>
+        <v>5961308.435321876</v>
       </c>
       <c r="U7" t="n">
         <v>3100813.405939738</v>
@@ -1818,7 +2055,7 @@
         <v>102034570</v>
       </c>
       <c r="H8" t="n">
-        <v>3498352195.128958</v>
+        <v>3498352195.128959</v>
       </c>
       <c r="I8" t="n">
         <v>3620494120.208659</v>
@@ -1836,7 +2073,7 @@
         <v>8670037791.957762</v>
       </c>
       <c r="N8" t="n">
-        <v>2984088244.81701</v>
+        <v>2984088244.817011</v>
       </c>
       <c r="O8" t="n">
         <v>3468110851.32194</v>
@@ -1854,7 +2091,7 @@
         <v>19210162807.07394</v>
       </c>
       <c r="T8" t="n">
-        <v>9887988.707245303</v>
+        <v>9887988.7072453</v>
       </c>
       <c r="U8" t="n">
         <v>4670172.061946869</v>
@@ -1915,7 +2152,7 @@
         <v>18257388784.49911</v>
       </c>
       <c r="N9" t="n">
-        <v>5147033065.680119</v>
+        <v>5147033065.680115</v>
       </c>
       <c r="O9" t="n">
         <v>3271943745.566081</v>
@@ -1949,6 +2186,243 @@
       </c>
       <c r="Y9" t="n">
         <v>103847019.2706245</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>175647580.5315766</v>
+      </c>
+      <c r="C10" t="n">
+        <v>90376370.59467061</v>
+      </c>
+      <c r="D10" t="n">
+        <v>213820349.4378951</v>
+      </c>
+      <c r="E10" t="n">
+        <v>146923458.4059441</v>
+      </c>
+      <c r="F10" t="n">
+        <v>117199435837.548</v>
+      </c>
+      <c r="G10" t="n">
+        <v>210307323</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7957744900.626878</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6199141826.733073</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11164814243.38097</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4336149033.751409</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5191776377339.425</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11372805096.2049</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10386892305.29515</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9029090399.948893</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7462015146.989143</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>10428908768.45368</v>
+      </c>
+      <c r="R10" t="n">
+        <v>596510040468.7063</v>
+      </c>
+      <c r="S10" t="n">
+        <v>36630898821.89375</v>
+      </c>
+      <c r="T10" t="n">
+        <v>52840634.10264293</v>
+      </c>
+      <c r="U10" t="n">
+        <v>43400625.05702718</v>
+      </c>
+      <c r="V10" t="n">
+        <v>23011413.67906871</v>
+      </c>
+      <c r="W10" t="n">
+        <v>42759012.79789517</v>
+      </c>
+      <c r="X10" t="n">
+        <v>35325980536.64599</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>106659743.1822421</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>372630597.8047811</v>
+      </c>
+      <c r="C11" t="n">
+        <v>606406777.9172617</v>
+      </c>
+      <c r="D11" t="n">
+        <v>364843362.8226473</v>
+      </c>
+      <c r="E11" t="n">
+        <v>317448292.3816548</v>
+      </c>
+      <c r="F11" t="n">
+        <v>325272176521.1472</v>
+      </c>
+      <c r="G11" t="n">
+        <v>635187753</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11691006795.8308</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8970982479.430338</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3381395533.961497</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3474125579.106647</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11579812330066.04</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15342029845.0944</v>
+      </c>
+      <c r="N11" t="n">
+        <v>27077784588.4658</v>
+      </c>
+      <c r="O11" t="n">
+        <v>13892577130.80762</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8727998729.923687</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>19163072414.63404</v>
+      </c>
+      <c r="R11" t="n">
+        <v>965574514892.479</v>
+      </c>
+      <c r="S11" t="n">
+        <v>45002332481.52705</v>
+      </c>
+      <c r="T11" t="n">
+        <v>54749608.22585229</v>
+      </c>
+      <c r="U11" t="n">
+        <v>75279716.0410258</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10312893.4181177</v>
+      </c>
+      <c r="W11" t="n">
+        <v>28875322.11744221</v>
+      </c>
+      <c r="X11" t="n">
+        <v>104306517017.2542</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>64061503.57772753</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>922589630.0857264</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1130583621.496643</v>
+      </c>
+      <c r="D12" t="n">
+        <v>913007011.8065654</v>
+      </c>
+      <c r="E12" t="n">
+        <v>858185295.404788</v>
+      </c>
+      <c r="F12" t="n">
+        <v>567633990513.5776</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1575327651</v>
+      </c>
+      <c r="H12" t="n">
+        <v>30560451325.96666</v>
+      </c>
+      <c r="I12" t="n">
+        <v>20167926607.62239</v>
+      </c>
+      <c r="J12" t="n">
+        <v>11380706589.21525</v>
+      </c>
+      <c r="K12" t="n">
+        <v>15588206261.01287</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13223070788585.14</v>
+      </c>
+      <c r="M12" t="n">
+        <v>61895444363.27143</v>
+      </c>
+      <c r="N12" t="n">
+        <v>41702935529.07892</v>
+      </c>
+      <c r="O12" t="n">
+        <v>28212818044.71777</v>
+      </c>
+      <c r="P12" t="n">
+        <v>14990236986.25175</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>37519153060.88023</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3547974876823.054</v>
+      </c>
+      <c r="S12" t="n">
+        <v>63149420439.56248</v>
+      </c>
+      <c r="T12" t="n">
+        <v>53063800.2422708</v>
+      </c>
+      <c r="U12" t="n">
+        <v>20389836.02638881</v>
+      </c>
+      <c r="V12" t="n">
+        <v>16942307.19701349</v>
+      </c>
+      <c r="W12" t="n">
+        <v>39180611.36930978</v>
+      </c>
+      <c r="X12" t="n">
+        <v>167044750326.2195</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>133548763.8659393</v>
       </c>
     </row>
   </sheetData>
@@ -1962,7 +2436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2196,7 +2670,7 @@
         <v>22366.05289272115</v>
       </c>
       <c r="H3" t="n">
-        <v>39686.39085698952</v>
+        <v>39686.39085698951</v>
       </c>
       <c r="I3" t="n">
         <v>73457.30324147111</v>
@@ -2257,7 +2731,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3421.783682487306</v>
+        <v>3421.783682487301</v>
       </c>
       <c r="C4" t="n">
         <v>2078.210691826355</v>
@@ -2275,7 +2749,7 @@
         <v>21507.42040939979</v>
       </c>
       <c r="H4" t="n">
-        <v>51040.96178421154</v>
+        <v>51040.96178421153</v>
       </c>
       <c r="I4" t="n">
         <v>117177.0227814508</v>
@@ -2311,7 +2785,7 @@
         <v>110033.7595778716</v>
       </c>
       <c r="T4" t="n">
-        <v>2965.810058461386</v>
+        <v>2965.810058461384</v>
       </c>
       <c r="U4" t="n">
         <v>3002.777135925468</v>
@@ -2336,7 +2810,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6266.653908676285</v>
+        <v>6266.653908676292</v>
       </c>
       <c r="C5" t="n">
         <v>1831.226876410785</v>
@@ -2415,7 +2889,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5074.254542595255</v>
+        <v>5074.254542595254</v>
       </c>
       <c r="C6" t="n">
         <v>5792.631280138497</v>
@@ -2451,7 +2925,7 @@
         <v>23353.82600566547</v>
       </c>
       <c r="N6" t="n">
-        <v>40410.71252213961</v>
+        <v>40410.71252213968</v>
       </c>
       <c r="O6" t="n">
         <v>65853.40453576544</v>
@@ -2469,7 +2943,7 @@
         <v>60582.66217844582</v>
       </c>
       <c r="T6" t="n">
-        <v>1978.266220495668</v>
+        <v>1978.266220495672</v>
       </c>
       <c r="U6" t="n">
         <v>2140.915383734092</v>
@@ -2494,7 +2968,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5289.089288037948</v>
+        <v>5289.089288037956</v>
       </c>
       <c r="C7" t="n">
         <v>4158.025270291973</v>
@@ -2530,7 +3004,7 @@
         <v>32653.40434540355</v>
       </c>
       <c r="N7" t="n">
-        <v>37142.13120315568</v>
+        <v>37142.1312031557</v>
       </c>
       <c r="O7" t="n">
         <v>51558.42293123015</v>
@@ -2548,7 +3022,7 @@
         <v>92216.67448102927</v>
       </c>
       <c r="T7" t="n">
-        <v>2441.579086436045</v>
+        <v>2441.579086436046</v>
       </c>
       <c r="U7" t="n">
         <v>1760.912662780224</v>
@@ -2591,7 +3065,7 @@
         <v>10101.21626340115</v>
       </c>
       <c r="H8" t="n">
-        <v>59146.86969847989</v>
+        <v>59146.8696984799</v>
       </c>
       <c r="I8" t="n">
         <v>60170.54196372722</v>
@@ -2609,7 +3083,7 @@
         <v>93113.03771200766</v>
       </c>
       <c r="N8" t="n">
-        <v>54626.80884709458</v>
+        <v>54626.80884709459</v>
       </c>
       <c r="O8" t="n">
         <v>58890.66862688808</v>
@@ -2627,7 +3101,7 @@
         <v>138600.7316253199</v>
       </c>
       <c r="T8" t="n">
-        <v>3144.517245499745</v>
+        <v>3144.517245499744</v>
       </c>
       <c r="U8" t="n">
         <v>2161.05808851749</v>
@@ -2688,7 +3162,7 @@
         <v>135119.9052119972</v>
       </c>
       <c r="N9" t="n">
-        <v>71742.8258830116</v>
+        <v>71742.82588301157</v>
       </c>
       <c r="O9" t="n">
         <v>57200.90685964761</v>
@@ -2722,6 +3196,243 @@
       </c>
       <c r="Y9" t="n">
         <v>10190.53576955719</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>13253.21019721549</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9506.648757299841</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14622.59721930051</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12121.19871984385</v>
+      </c>
+      <c r="F10" t="n">
+        <v>342344.0314034232</v>
+      </c>
+      <c r="G10" t="n">
+        <v>14501.97652046093</v>
+      </c>
+      <c r="H10" t="n">
+        <v>89206.19317416743</v>
+      </c>
+      <c r="I10" t="n">
+        <v>78734.62914584074</v>
+      </c>
+      <c r="J10" t="n">
+        <v>105663.6846006279</v>
+      </c>
+      <c r="K10" t="n">
+        <v>65849.44216735179</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2278546.988178963</v>
+      </c>
+      <c r="M10" t="n">
+        <v>106643.3546743767</v>
+      </c>
+      <c r="N10" t="n">
+        <v>101916.1042490104</v>
+      </c>
+      <c r="O10" t="n">
+        <v>95021.52598200522</v>
+      </c>
+      <c r="P10" t="n">
+        <v>86382.95634550338</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>102122.028810897</v>
+      </c>
+      <c r="R10" t="n">
+        <v>772340.6246396122</v>
+      </c>
+      <c r="S10" t="n">
+        <v>191392.0030249272</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7269.156354257551</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6587.915076640498</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4797.021334022678</v>
+      </c>
+      <c r="W10" t="n">
+        <v>6539.037604869326</v>
+      </c>
+      <c r="X10" t="n">
+        <v>187952.0697854801</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10327.62040269888</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>19303.64208652816</v>
+      </c>
+      <c r="C11" t="n">
+        <v>24625.32797583134</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19100.87335235348</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17817.07867136627</v>
+      </c>
+      <c r="F11" t="n">
+        <v>570326.3771921715</v>
+      </c>
+      <c r="G11" t="n">
+        <v>25202.93143664046</v>
+      </c>
+      <c r="H11" t="n">
+        <v>108124.9591714642</v>
+      </c>
+      <c r="I11" t="n">
+        <v>94715.27057148883</v>
+      </c>
+      <c r="J11" t="n">
+        <v>58149.76813334251</v>
+      </c>
+      <c r="K11" t="n">
+        <v>58941.71340491085</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3402912.330646507</v>
+      </c>
+      <c r="M11" t="n">
+        <v>123862.9478298268</v>
+      </c>
+      <c r="N11" t="n">
+        <v>164553.2879904434</v>
+      </c>
+      <c r="O11" t="n">
+        <v>117866.7770442868</v>
+      </c>
+      <c r="P11" t="n">
+        <v>93423.75891561892</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>138430.7495270977</v>
+      </c>
+      <c r="R11" t="n">
+        <v>982636.5120900398</v>
+      </c>
+      <c r="S11" t="n">
+        <v>212137.531996408</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7399.297819783462</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8676.388421516513</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3211.369399199927</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5373.576287486966</v>
+      </c>
+      <c r="X11" t="n">
+        <v>322965.1947458954</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8003.843050543129</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>30374.16056594365</v>
+      </c>
+      <c r="C12" t="n">
+        <v>33624.15235357827</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30216.00588771728</v>
+      </c>
+      <c r="E12" t="n">
+        <v>29294.79980141165</v>
+      </c>
+      <c r="F12" t="n">
+        <v>753414.8860445868</v>
+      </c>
+      <c r="G12" t="n">
+        <v>39690.39746588588</v>
+      </c>
+      <c r="H12" t="n">
+        <v>174815.4779359272</v>
+      </c>
+      <c r="I12" t="n">
+        <v>142013.8254101424</v>
+      </c>
+      <c r="J12" t="n">
+        <v>106680.3945868933</v>
+      </c>
+      <c r="K12" t="n">
+        <v>124852.7383000184</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3636354.051599644</v>
+      </c>
+      <c r="M12" t="n">
+        <v>248787.9505990421</v>
+      </c>
+      <c r="N12" t="n">
+        <v>204212.9661140029</v>
+      </c>
+      <c r="O12" t="n">
+        <v>167966.7170742995</v>
+      </c>
+      <c r="P12" t="n">
+        <v>122434.6233148603</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>193698.6139880206</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1883606.879585827</v>
+      </c>
+      <c r="S12" t="n">
+        <v>251295.4843198789</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7284.490390018426</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4515.510605279186</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4116.103399698979</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6259.441777771383</v>
+      </c>
+      <c r="X12" t="n">
+        <v>408711.0841734287</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11556.33003448496</v>
       </c>
     </row>
   </sheetData>
@@ -2735,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3030,7 +3741,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.345265714000432</v>
+        <v>5.345265714000422</v>
       </c>
       <c r="C4" t="n">
         <v>3.61971983471546</v>
@@ -3109,7 +3820,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.12997670376767</v>
+        <v>11.12997670376768</v>
       </c>
       <c r="C5" t="n">
         <v>3.364917480840423</v>
@@ -3188,7 +3899,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.715084656748198</v>
+        <v>9.715084656748189</v>
       </c>
       <c r="C6" t="n">
         <v>10.20303101822702</v>
@@ -3224,7 +3935,7 @@
         <v>7.162204211097505</v>
       </c>
       <c r="N6" t="n">
-        <v>6.855005696756391</v>
+        <v>6.855005696756401</v>
       </c>
       <c r="O6" t="n">
         <v>12.34262583221478</v>
@@ -3242,7 +3953,7 @@
         <v>10.94156780049854</v>
       </c>
       <c r="T6" t="n">
-        <v>6.901753797185652</v>
+        <v>6.901753797185664</v>
       </c>
       <c r="U6" t="n">
         <v>7.565446964732929</v>
@@ -3267,7 +3978,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.573196339785156</v>
+        <v>9.573196339785166</v>
       </c>
       <c r="C7" t="n">
         <v>8.574333616813329</v>
@@ -3303,7 +4014,7 @@
         <v>11.31530867562364</v>
       </c>
       <c r="N7" t="n">
-        <v>6.6767650761424</v>
+        <v>6.676765076142405</v>
       </c>
       <c r="O7" t="n">
         <v>8.409128756017719</v>
@@ -3321,7 +4032,7 @@
         <v>15.3610396460105</v>
       </c>
       <c r="T7" t="n">
-        <v>7.8771681937003</v>
+        <v>7.877168193700309</v>
       </c>
       <c r="U7" t="n">
         <v>5.81562156694716</v>
@@ -3364,7 +4075,7 @@
         <v>16.78120305942506</v>
       </c>
       <c r="H8" t="n">
-        <v>11.33716187820805</v>
+        <v>11.33716187820806</v>
       </c>
       <c r="I8" t="n">
         <v>9.591498048199464</v>
@@ -3382,7 +4093,7 @@
         <v>19.58476580228633</v>
       </c>
       <c r="N8" t="n">
-        <v>9.786751488956265</v>
+        <v>9.78675148895627</v>
       </c>
       <c r="O8" t="n">
         <v>9.735149338341314</v>
@@ -3400,7 +4111,7 @@
         <v>24.03597018976452</v>
       </c>
       <c r="T8" t="n">
-        <v>8.414887820570316</v>
+        <v>8.414887820570312</v>
       </c>
       <c r="U8" t="n">
         <v>6.168853038880812</v>
@@ -3495,6 +4206,243 @@
       </c>
       <c r="Y9" t="n">
         <v>26.68867374117026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>32.09257365449766</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22.68441234299554</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35.19096043630014</v>
+      </c>
+      <c r="E10" t="n">
+        <v>20.19672986718173</v>
+      </c>
+      <c r="F10" t="n">
+        <v>707.946786377546</v>
+      </c>
+      <c r="G10" t="n">
+        <v>35.12513849754712</v>
+      </c>
+      <c r="H10" t="n">
+        <v>20.44162596226064</v>
+      </c>
+      <c r="I10" t="n">
+        <v>15.50124186398994</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24.69399604008278</v>
+      </c>
+      <c r="K10" t="n">
+        <v>18.29922517489014</v>
+      </c>
+      <c r="L10" t="n">
+        <v>565.2599741731888</v>
+      </c>
+      <c r="M10" t="n">
+        <v>27.67412076011604</v>
+      </c>
+      <c r="N10" t="n">
+        <v>31.59913271317306</v>
+      </c>
+      <c r="O10" t="n">
+        <v>29.22249417649837</v>
+      </c>
+      <c r="P10" t="n">
+        <v>16.4793000733312</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>30.57816075759419</v>
+      </c>
+      <c r="R10" t="n">
+        <v>228.3620560060585</v>
+      </c>
+      <c r="S10" t="n">
+        <v>48.6502884410807</v>
+      </c>
+      <c r="T10" t="n">
+        <v>32.24449418779276</v>
+      </c>
+      <c r="U10" t="n">
+        <v>31.02885054739412</v>
+      </c>
+      <c r="V10" t="n">
+        <v>15.81998582037875</v>
+      </c>
+      <c r="W10" t="n">
+        <v>23.64014478017123</v>
+      </c>
+      <c r="X10" t="n">
+        <v>791.6047463376083</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>38.08864318487765</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>59.65596970526536</v>
+      </c>
+      <c r="C11" t="n">
+        <v>74.18064234496207</v>
+      </c>
+      <c r="D11" t="n">
+        <v>59.88814978922026</v>
+      </c>
+      <c r="E11" t="n">
+        <v>54.58596065801887</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1711.987210858065</v>
+      </c>
+      <c r="G11" t="n">
+        <v>77.31089133281878</v>
+      </c>
+      <c r="H11" t="n">
+        <v>38.88713772582025</v>
+      </c>
+      <c r="I11" t="n">
+        <v>33.46364262822199</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.58264489373508</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20.68665990310879</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1129.795433205618</v>
+      </c>
+      <c r="M11" t="n">
+        <v>44.52788225952673</v>
+      </c>
+      <c r="N11" t="n">
+        <v>69.05529141383447</v>
+      </c>
+      <c r="O11" t="n">
+        <v>50.21502320963754</v>
+      </c>
+      <c r="P11" t="n">
+        <v>28.54993201799183</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>57.82517563202006</v>
+      </c>
+      <c r="R11" t="n">
+        <v>370.1752129496237</v>
+      </c>
+      <c r="S11" t="n">
+        <v>89.01314252601313</v>
+      </c>
+      <c r="T11" t="n">
+        <v>36.34928824899742</v>
+      </c>
+      <c r="U11" t="n">
+        <v>39.78977654229446</v>
+      </c>
+      <c r="V11" t="n">
+        <v>12.61567410377586</v>
+      </c>
+      <c r="W11" t="n">
+        <v>22.21777213232927</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1746.023120768679</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>40.69252170884064</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>177.871429502445</v>
+      </c>
+      <c r="C12" t="n">
+        <v>196.5435921355121</v>
+      </c>
+      <c r="D12" t="n">
+        <v>183.0251233418866</v>
+      </c>
+      <c r="E12" t="n">
+        <v>177.0301035088983</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4177.840880281125</v>
+      </c>
+      <c r="G12" t="n">
+        <v>235.6541031665305</v>
+      </c>
+      <c r="H12" t="n">
+        <v>115.8431003919654</v>
+      </c>
+      <c r="I12" t="n">
+        <v>92.37035338833097</v>
+      </c>
+      <c r="J12" t="n">
+        <v>71.08020360896873</v>
+      </c>
+      <c r="K12" t="n">
+        <v>82.83291796273238</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2239.876220919736</v>
+      </c>
+      <c r="M12" t="n">
+        <v>164.4551252517821</v>
+      </c>
+      <c r="N12" t="n">
+        <v>115.1021407560359</v>
+      </c>
+      <c r="O12" t="n">
+        <v>97.5134851747312</v>
+      </c>
+      <c r="P12" t="n">
+        <v>61.90866634822223</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>112.4654796872119</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1024.739484983219</v>
+      </c>
+      <c r="S12" t="n">
+        <v>146.2114039732248</v>
+      </c>
+      <c r="T12" t="n">
+        <v>58.89521625563781</v>
+      </c>
+      <c r="U12" t="n">
+        <v>35.93272438798667</v>
+      </c>
+      <c r="V12" t="n">
+        <v>32.64355458932106</v>
+      </c>
+      <c r="W12" t="n">
+        <v>50.01211659418253</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3206.877803856305</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>92.48109899280364</v>
       </c>
     </row>
   </sheetData>

--- a/wfcv_errors.xlsx
+++ b/wfcv_errors.xlsx
@@ -650,7 +650,7 @@
         <v>20216.66666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>33010.0813098197</v>
+        <v>33010.08130981971</v>
       </c>
       <c r="I3" t="n">
         <v>62628.40625</v>
@@ -747,7 +747,7 @@
         <v>124410.610197756</v>
       </c>
       <c r="N4" t="n">
-        <v>51237.71816595436</v>
+        <v>51237.71816595434</v>
       </c>
       <c r="O4" t="n">
         <v>31007.625</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4903.130554260567</v>
+        <v>4903.130554260562</v>
       </c>
       <c r="C5" t="n">
         <v>1506.654947916667</v>
@@ -905,7 +905,7 @@
         <v>18991.37853657941</v>
       </c>
       <c r="N6" t="n">
-        <v>36046.26910584789</v>
+        <v>36046.26910584787</v>
       </c>
       <c r="O6" t="n">
         <v>64902.41666666666</v>
@@ -923,7 +923,7 @@
         <v>57851.1291583091</v>
       </c>
       <c r="T6" t="n">
-        <v>1865.779971741221</v>
+        <v>1865.779971741217</v>
       </c>
       <c r="U6" t="n">
         <v>1901.279296875</v>
@@ -966,7 +966,7 @@
         <v>5790</v>
       </c>
       <c r="H7" t="n">
-        <v>42413.09713300135</v>
+        <v>42413.09713300133</v>
       </c>
       <c r="I7" t="n">
         <v>76646.91666666667</v>
@@ -984,7 +984,7 @@
         <v>30311.20154526455</v>
       </c>
       <c r="N7" t="n">
-        <v>35751.69722979813</v>
+        <v>35751.6972297981</v>
       </c>
       <c r="O7" t="n">
         <v>44879.83333333334</v>
@@ -1002,7 +1002,7 @@
         <v>82475.4093490758</v>
       </c>
       <c r="T7" t="n">
-        <v>2176.050840488229</v>
+        <v>2176.050840488226</v>
       </c>
       <c r="U7" t="n">
         <v>1603.23046875</v>
@@ -1063,7 +1063,7 @@
         <v>73236.62464174563</v>
       </c>
       <c r="N8" t="n">
-        <v>53527.76611976931</v>
+        <v>53527.76611976929</v>
       </c>
       <c r="O8" t="n">
         <v>53437.63541666666</v>
@@ -1160,7 +1160,7 @@
         <v>179783.4296532094</v>
       </c>
       <c r="T9" t="n">
-        <v>4672.590531783036</v>
+        <v>4672.590531783037</v>
       </c>
       <c r="U9" t="n">
         <v>2930.623697916667</v>
@@ -1203,7 +1203,7 @@
         <v>13235</v>
       </c>
       <c r="H10" t="n">
-        <v>80597.60424170281</v>
+        <v>80597.60424170278</v>
       </c>
       <c r="I10" t="n">
         <v>65357.1875</v>
@@ -1239,7 +1239,7 @@
         <v>188461.891614156</v>
       </c>
       <c r="T10" t="n">
-        <v>7101.126866522368</v>
+        <v>7101.126866522369</v>
       </c>
       <c r="U10" t="n">
         <v>6031.252604166667</v>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30045.9692099567</v>
+        <v>30045.96920995669</v>
       </c>
       <c r="C12" t="n">
         <v>33288.51302083334</v>
@@ -1660,7 +1660,7 @@
         <v>500240322</v>
       </c>
       <c r="H3" t="n">
-        <v>1575009619.253741</v>
+        <v>1575009619.253742</v>
       </c>
       <c r="I3" t="n">
         <v>5395975399.50944</v>
@@ -1739,7 +1739,7 @@
         <v>462569132.6666667</v>
       </c>
       <c r="H4" t="n">
-        <v>2605179779.857342</v>
+        <v>2605179779.857343</v>
       </c>
       <c r="I4" t="n">
         <v>13730454667.92464</v>
@@ -1757,7 +1757,7 @@
         <v>16149525145.71921</v>
       </c>
       <c r="N4" t="n">
-        <v>3444492794.65529</v>
+        <v>3444492794.655289</v>
       </c>
       <c r="O4" t="n">
         <v>2127819744.307292</v>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39270951.21112785</v>
+        <v>39270951.21112776</v>
       </c>
       <c r="C5" t="n">
         <v>3353391.872889201</v>
@@ -1915,7 +1915,7 @@
         <v>545401189.1028966</v>
       </c>
       <c r="N6" t="n">
-        <v>1633025686.547017</v>
+        <v>1633025686.547016</v>
       </c>
       <c r="O6" t="n">
         <v>4336670888.951172</v>
@@ -1933,7 +1933,7 @@
         <v>3670258956.62769</v>
       </c>
       <c r="T6" t="n">
-        <v>3913537.239154231</v>
+        <v>3913537.239154214</v>
       </c>
       <c r="U6" t="n">
         <v>4583518.680309296</v>
@@ -1976,7 +1976,7 @@
         <v>42854984.66666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2562884499.72222</v>
+        <v>2562884499.722218</v>
       </c>
       <c r="I7" t="n">
         <v>6180204224.302083</v>
@@ -1994,7 +1994,7 @@
         <v>1066244815.344419</v>
       </c>
       <c r="N7" t="n">
-        <v>1379537910.312433</v>
+        <v>1379537910.312431</v>
       </c>
       <c r="O7" t="n">
         <v>2658270975.155599</v>
@@ -2012,7 +2012,7 @@
         <v>8503915052.340116</v>
       </c>
       <c r="T7" t="n">
-        <v>5961308.435321876</v>
+        <v>5961308.43532186</v>
       </c>
       <c r="U7" t="n">
         <v>3100813.405939738</v>
@@ -2055,7 +2055,7 @@
         <v>102034570</v>
       </c>
       <c r="H8" t="n">
-        <v>3498352195.128959</v>
+        <v>3498352195.128962</v>
       </c>
       <c r="I8" t="n">
         <v>3620494120.208659</v>
@@ -2073,7 +2073,7 @@
         <v>8670037791.957762</v>
       </c>
       <c r="N8" t="n">
-        <v>2984088244.817011</v>
+        <v>2984088244.81701</v>
       </c>
       <c r="O8" t="n">
         <v>3468110851.32194</v>
@@ -2170,7 +2170,7 @@
         <v>33502880783.28843</v>
       </c>
       <c r="T9" t="n">
-        <v>33420474.073695</v>
+        <v>33420474.07369502</v>
       </c>
       <c r="U9" t="n">
         <v>11783387.28980001</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>175647580.5315766</v>
+        <v>175647580.5315764</v>
       </c>
       <c r="C10" t="n">
         <v>90376370.59467061</v>
@@ -2213,7 +2213,7 @@
         <v>210307323</v>
       </c>
       <c r="H10" t="n">
-        <v>7957744900.626878</v>
+        <v>7957744900.626874</v>
       </c>
       <c r="I10" t="n">
         <v>6199141826.733073</v>
@@ -2249,7 +2249,7 @@
         <v>36630898821.89375</v>
       </c>
       <c r="T10" t="n">
-        <v>52840634.10264293</v>
+        <v>52840634.10264295</v>
       </c>
       <c r="U10" t="n">
         <v>43400625.05702718</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>922589630.0857264</v>
+        <v>922589630.0857261</v>
       </c>
       <c r="C12" t="n">
         <v>1130583621.496643</v>
@@ -2371,7 +2371,7 @@
         <v>1575327651</v>
       </c>
       <c r="H12" t="n">
-        <v>30560451325.96666</v>
+        <v>30560451325.96665</v>
       </c>
       <c r="I12" t="n">
         <v>20167926607.62239</v>
@@ -2670,7 +2670,7 @@
         <v>22366.05289272115</v>
       </c>
       <c r="H3" t="n">
-        <v>39686.39085698951</v>
+        <v>39686.39085698952</v>
       </c>
       <c r="I3" t="n">
         <v>73457.30324147111</v>
@@ -2749,7 +2749,7 @@
         <v>21507.42040939979</v>
       </c>
       <c r="H4" t="n">
-        <v>51040.96178421153</v>
+        <v>51040.96178421154</v>
       </c>
       <c r="I4" t="n">
         <v>117177.0227814508</v>
@@ -2767,7 +2767,7 @@
         <v>127080.7819684755</v>
       </c>
       <c r="N4" t="n">
-        <v>58689.80145353441</v>
+        <v>58689.8014535344</v>
       </c>
       <c r="O4" t="n">
         <v>46128.29656845451</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6266.653908676292</v>
+        <v>6266.653908676285</v>
       </c>
       <c r="C5" t="n">
         <v>1831.226876410785</v>
@@ -2925,7 +2925,7 @@
         <v>23353.82600566547</v>
       </c>
       <c r="N6" t="n">
-        <v>40410.71252213968</v>
+        <v>40410.71252213967</v>
       </c>
       <c r="O6" t="n">
         <v>65853.40453576544</v>
@@ -2943,7 +2943,7 @@
         <v>60582.66217844582</v>
       </c>
       <c r="T6" t="n">
-        <v>1978.266220495672</v>
+        <v>1978.266220495668</v>
       </c>
       <c r="U6" t="n">
         <v>2140.915383734092</v>
@@ -2986,7 +2986,7 @@
         <v>6546.371870484189</v>
       </c>
       <c r="H7" t="n">
-        <v>50624.93950339319</v>
+        <v>50624.93950339317</v>
       </c>
       <c r="I7" t="n">
         <v>78614.27493974668</v>
@@ -3004,7 +3004,7 @@
         <v>32653.40434540355</v>
       </c>
       <c r="N7" t="n">
-        <v>37142.1312031557</v>
+        <v>37142.13120315568</v>
       </c>
       <c r="O7" t="n">
         <v>51558.42293123015</v>
@@ -3022,7 +3022,7 @@
         <v>92216.67448102927</v>
       </c>
       <c r="T7" t="n">
-        <v>2441.579086436046</v>
+        <v>2441.579086436042</v>
       </c>
       <c r="U7" t="n">
         <v>1760.912662780224</v>
@@ -3065,7 +3065,7 @@
         <v>10101.21626340115</v>
       </c>
       <c r="H8" t="n">
-        <v>59146.8696984799</v>
+        <v>59146.86969847992</v>
       </c>
       <c r="I8" t="n">
         <v>60170.54196372722</v>
@@ -3083,7 +3083,7 @@
         <v>93113.03771200766</v>
       </c>
       <c r="N8" t="n">
-        <v>54626.80884709459</v>
+        <v>54626.80884709458</v>
       </c>
       <c r="O8" t="n">
         <v>58890.66862688808</v>
@@ -3180,7 +3180,7 @@
         <v>183037.9217082855</v>
       </c>
       <c r="T9" t="n">
-        <v>5781.044375689828</v>
+        <v>5781.04437568983</v>
       </c>
       <c r="U9" t="n">
         <v>3432.693882332068</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13253.21019721549</v>
+        <v>13253.21019721548</v>
       </c>
       <c r="C10" t="n">
         <v>9506.648757299841</v>
@@ -3223,7 +3223,7 @@
         <v>14501.97652046093</v>
       </c>
       <c r="H10" t="n">
-        <v>89206.19317416743</v>
+        <v>89206.19317416742</v>
       </c>
       <c r="I10" t="n">
         <v>78734.62914584074</v>
@@ -3259,7 +3259,7 @@
         <v>191392.0030249272</v>
       </c>
       <c r="T10" t="n">
-        <v>7269.156354257551</v>
+        <v>7269.156354257552</v>
       </c>
       <c r="U10" t="n">
         <v>6587.915076640498</v>
@@ -3777,7 +3777,7 @@
         <v>41.47238070599524</v>
       </c>
       <c r="N4" t="n">
-        <v>9.911764235633051</v>
+        <v>9.911764235633045</v>
       </c>
       <c r="O4" t="n">
         <v>5.952073234211847</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.12997670376768</v>
+        <v>11.12997670376767</v>
       </c>
       <c r="C5" t="n">
         <v>3.364917480840423</v>
@@ -3935,7 +3935,7 @@
         <v>7.162204211097505</v>
       </c>
       <c r="N6" t="n">
-        <v>6.855005696756401</v>
+        <v>6.855005696756399</v>
       </c>
       <c r="O6" t="n">
         <v>12.34262583221478</v>
@@ -3953,7 +3953,7 @@
         <v>10.94156780049854</v>
       </c>
       <c r="T6" t="n">
-        <v>6.901753797185664</v>
+        <v>6.901753797185652</v>
       </c>
       <c r="U6" t="n">
         <v>7.565446964732929</v>
@@ -4014,7 +4014,7 @@
         <v>11.31530867562364</v>
       </c>
       <c r="N7" t="n">
-        <v>6.676765076142405</v>
+        <v>6.6767650761424</v>
       </c>
       <c r="O7" t="n">
         <v>8.409128756017719</v>
@@ -4032,7 +4032,7 @@
         <v>15.3610396460105</v>
       </c>
       <c r="T7" t="n">
-        <v>7.877168193700309</v>
+        <v>7.8771681937003</v>
       </c>
       <c r="U7" t="n">
         <v>5.81562156694716</v>
@@ -4093,7 +4093,7 @@
         <v>19.58476580228633</v>
       </c>
       <c r="N8" t="n">
-        <v>9.78675148895627</v>
+        <v>9.786751488956265</v>
       </c>
       <c r="O8" t="n">
         <v>9.735149338341314</v>
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.09257365449766</v>
+        <v>32.09257365449764</v>
       </c>
       <c r="C10" t="n">
         <v>22.68441234299554</v>
@@ -4233,7 +4233,7 @@
         <v>35.12513849754712</v>
       </c>
       <c r="H10" t="n">
-        <v>20.44162596226064</v>
+        <v>20.44162596226063</v>
       </c>
       <c r="I10" t="n">
         <v>15.50124186398994</v>
@@ -4269,7 +4269,7 @@
         <v>48.6502884410807</v>
       </c>
       <c r="T10" t="n">
-        <v>32.24449418779276</v>
+        <v>32.24449418779277</v>
       </c>
       <c r="U10" t="n">
         <v>31.02885054739412</v>

--- a/wfcv_errors.xlsx
+++ b/wfcv_errors.xlsx
@@ -571,7 +571,7 @@
         <v>13707.66666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>72184.56343936159</v>
+        <v>72184.56343936158</v>
       </c>
       <c r="I2" t="n">
         <v>82854.29427083333</v>
@@ -607,7 +607,7 @@
         <v>60625.59660194017</v>
       </c>
       <c r="T2" t="n">
-        <v>1684.271403184775</v>
+        <v>1684.271403184777</v>
       </c>
       <c r="U2" t="n">
         <v>902.5696614583334</v>
@@ -668,7 +668,7 @@
         <v>77247.78947712778</v>
       </c>
       <c r="N3" t="n">
-        <v>35367.93689327795</v>
+        <v>35367.93689327798</v>
       </c>
       <c r="O3" t="n">
         <v>51755.71875</v>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2534.952297138041</v>
+        <v>2534.952297138043</v>
       </c>
       <c r="C4" t="n">
         <v>1846.123697916667</v>
@@ -747,7 +747,7 @@
         <v>124410.610197756</v>
       </c>
       <c r="N4" t="n">
-        <v>51237.71816595434</v>
+        <v>51237.71816595438</v>
       </c>
       <c r="O4" t="n">
         <v>31007.625</v>
@@ -765,7 +765,7 @@
         <v>109694.893124569</v>
       </c>
       <c r="T4" t="n">
-        <v>2501.413806156803</v>
+        <v>2501.413806156802</v>
       </c>
       <c r="U4" t="n">
         <v>2046.853515625</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4903.130554260562</v>
+        <v>4903.130554260567</v>
       </c>
       <c r="C5" t="n">
         <v>1506.654947916667</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4364.963870032744</v>
+        <v>4364.963870032741</v>
       </c>
       <c r="C6" t="n">
         <v>4696.81640625</v>
@@ -905,7 +905,7 @@
         <v>18991.37853657941</v>
       </c>
       <c r="N6" t="n">
-        <v>36046.26910584787</v>
+        <v>36046.26910584783</v>
       </c>
       <c r="O6" t="n">
         <v>64902.41666666666</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4241.459117188363</v>
+        <v>4241.459117188369</v>
       </c>
       <c r="C7" t="n">
         <v>3895.307291666667</v>
@@ -984,7 +984,7 @@
         <v>30311.20154526455</v>
       </c>
       <c r="N7" t="n">
-        <v>35751.6972297981</v>
+        <v>35751.69722979813</v>
       </c>
       <c r="O7" t="n">
         <v>44879.83333333334</v>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3746.133365116356</v>
+        <v>3746.133365116359</v>
       </c>
       <c r="C8" t="n">
         <v>3615.875</v>
@@ -1045,7 +1045,7 @@
         <v>9010.666666666666</v>
       </c>
       <c r="H8" t="n">
-        <v>43006.69727450333</v>
+        <v>43006.69727450332</v>
       </c>
       <c r="I8" t="n">
         <v>38301.96875</v>
@@ -1063,7 +1063,7 @@
         <v>73236.62464174563</v>
       </c>
       <c r="N8" t="n">
-        <v>53527.76611976929</v>
+        <v>53527.76611976925</v>
       </c>
       <c r="O8" t="n">
         <v>53437.63541666666</v>
@@ -1081,7 +1081,7 @@
         <v>131160.5307251292</v>
       </c>
       <c r="T8" t="n">
-        <v>2517.690965668588</v>
+        <v>2517.690965668587</v>
       </c>
       <c r="U8" t="n">
         <v>1749.504557291667</v>
@@ -1124,7 +1124,7 @@
         <v>9153</v>
       </c>
       <c r="H9" t="n">
-        <v>80066.32612700276</v>
+        <v>80066.32612700273</v>
       </c>
       <c r="I9" t="n">
         <v>89461.05208333333</v>
@@ -1160,7 +1160,7 @@
         <v>179783.4296532094</v>
       </c>
       <c r="T9" t="n">
-        <v>4672.590531783037</v>
+        <v>4672.590531783036</v>
       </c>
       <c r="U9" t="n">
         <v>2930.623697916667</v>
@@ -1203,7 +1203,7 @@
         <v>13235</v>
       </c>
       <c r="H10" t="n">
-        <v>80597.60424170278</v>
+        <v>80597.60424170281</v>
       </c>
       <c r="I10" t="n">
         <v>65357.1875</v>
@@ -1239,7 +1239,7 @@
         <v>188461.891614156</v>
       </c>
       <c r="T10" t="n">
-        <v>7101.126866522369</v>
+        <v>7101.126866522368</v>
       </c>
       <c r="U10" t="n">
         <v>6031.252604166667</v>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30045.96920995669</v>
+        <v>30045.9692099567</v>
       </c>
       <c r="C12" t="n">
         <v>33288.51302083334</v>
@@ -1397,7 +1397,7 @@
         <v>250038.5833333333</v>
       </c>
       <c r="T12" t="n">
-        <v>6799.315943783066</v>
+        <v>6799.315943783065</v>
       </c>
       <c r="U12" t="n">
         <v>4225.175130208333</v>
@@ -1617,7 +1617,7 @@
         <v>4011263734.364984</v>
       </c>
       <c r="T2" t="n">
-        <v>3106726.263457941</v>
+        <v>3106726.263457946</v>
       </c>
       <c r="U2" t="n">
         <v>1086386.527884166</v>
@@ -1678,7 +1678,7 @@
         <v>8445454670.066292</v>
       </c>
       <c r="N3" t="n">
-        <v>2604040124.042669</v>
+        <v>2604040124.042672</v>
       </c>
       <c r="O3" t="n">
         <v>3122885249.857096</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11708603.56973635</v>
+        <v>11708603.56973638</v>
       </c>
       <c r="C4" t="n">
         <v>4318959.679621379</v>
@@ -1757,7 +1757,7 @@
         <v>16149525145.71921</v>
       </c>
       <c r="N4" t="n">
-        <v>3444492794.655289</v>
+        <v>3444492794.655293</v>
       </c>
       <c r="O4" t="n">
         <v>2127819744.307292</v>
@@ -1775,7 +1775,7 @@
         <v>12107428246.84086</v>
       </c>
       <c r="T4" t="n">
-        <v>8796029.302870721</v>
+        <v>8796029.302870719</v>
       </c>
       <c r="U4" t="n">
         <v>9016670.528036753</v>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39270951.21112776</v>
+        <v>39270951.21112785</v>
       </c>
       <c r="C5" t="n">
         <v>3353391.872889201</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25748059.16304857</v>
+        <v>25748059.16304855</v>
       </c>
       <c r="C6" t="n">
         <v>33554577.14763895</v>
@@ -1915,7 +1915,7 @@
         <v>545401189.1028966</v>
       </c>
       <c r="N6" t="n">
-        <v>1633025686.547016</v>
+        <v>1633025686.547011</v>
       </c>
       <c r="O6" t="n">
         <v>4336670888.951172</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27974465.49683785</v>
+        <v>27974465.49683788</v>
       </c>
       <c r="C7" t="n">
         <v>17289174.14838664</v>
@@ -1994,7 +1994,7 @@
         <v>1066244815.344419</v>
       </c>
       <c r="N7" t="n">
-        <v>1379537910.312431</v>
+        <v>1379537910.312433</v>
       </c>
       <c r="O7" t="n">
         <v>2658270975.155599</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21828610.82480979</v>
+        <v>21828610.82480982</v>
       </c>
       <c r="C8" t="n">
         <v>19359147.61625163</v>
@@ -2055,7 +2055,7 @@
         <v>102034570</v>
       </c>
       <c r="H8" t="n">
-        <v>3498352195.128962</v>
+        <v>3498352195.128958</v>
       </c>
       <c r="I8" t="n">
         <v>3620494120.208659</v>
@@ -2073,7 +2073,7 @@
         <v>8670037791.957762</v>
       </c>
       <c r="N8" t="n">
-        <v>2984088244.81701</v>
+        <v>2984088244.817005</v>
       </c>
       <c r="O8" t="n">
         <v>3468110851.32194</v>
@@ -2091,7 +2091,7 @@
         <v>19210162807.07394</v>
       </c>
       <c r="T8" t="n">
-        <v>9887988.7072453</v>
+        <v>9887988.707245287</v>
       </c>
       <c r="U8" t="n">
         <v>4670172.061946869</v>
@@ -2134,7 +2134,7 @@
         <v>103443911</v>
       </c>
       <c r="H9" t="n">
-        <v>8667523496.573448</v>
+        <v>8667523496.573446</v>
       </c>
       <c r="I9" t="n">
         <v>10771272443.68522</v>
@@ -2170,7 +2170,7 @@
         <v>33502880783.28843</v>
       </c>
       <c r="T9" t="n">
-        <v>33420474.07369502</v>
+        <v>33420474.073695</v>
       </c>
       <c r="U9" t="n">
         <v>11783387.28980001</v>
@@ -2213,7 +2213,7 @@
         <v>210307323</v>
       </c>
       <c r="H10" t="n">
-        <v>7957744900.626874</v>
+        <v>7957744900.626878</v>
       </c>
       <c r="I10" t="n">
         <v>6199141826.733073</v>
@@ -2249,7 +2249,7 @@
         <v>36630898821.89375</v>
       </c>
       <c r="T10" t="n">
-        <v>52840634.10264295</v>
+        <v>52840634.10264293</v>
       </c>
       <c r="U10" t="n">
         <v>43400625.05702718</v>
@@ -2371,7 +2371,7 @@
         <v>1575327651</v>
       </c>
       <c r="H12" t="n">
-        <v>30560451325.96665</v>
+        <v>30560451325.96666</v>
       </c>
       <c r="I12" t="n">
         <v>20167926607.62239</v>
@@ -2389,7 +2389,7 @@
         <v>61895444363.27143</v>
       </c>
       <c r="N12" t="n">
-        <v>41702935529.07892</v>
+        <v>41702935529.07891</v>
       </c>
       <c r="O12" t="n">
         <v>28212818044.71777</v>
@@ -2407,7 +2407,7 @@
         <v>63149420439.56248</v>
       </c>
       <c r="T12" t="n">
-        <v>53063800.2422708</v>
+        <v>53063800.24227079</v>
       </c>
       <c r="U12" t="n">
         <v>20389836.02638881</v>
@@ -2627,7 +2627,7 @@
         <v>63334.53824229702</v>
       </c>
       <c r="T2" t="n">
-        <v>1762.590781621741</v>
+        <v>1762.590781621743</v>
       </c>
       <c r="U2" t="n">
         <v>1042.298674989163</v>
@@ -2688,7 +2688,7 @@
         <v>91899.15489310166</v>
       </c>
       <c r="N3" t="n">
-        <v>51029.79643348255</v>
+        <v>51029.79643348259</v>
       </c>
       <c r="O3" t="n">
         <v>55882.78133608864</v>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3421.783682487301</v>
+        <v>3421.783682487304</v>
       </c>
       <c r="C4" t="n">
         <v>2078.210691826355</v>
@@ -2767,7 +2767,7 @@
         <v>127080.7819684755</v>
       </c>
       <c r="N4" t="n">
-        <v>58689.8014535344</v>
+        <v>58689.80145353444</v>
       </c>
       <c r="O4" t="n">
         <v>46128.29656845451</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6266.653908676285</v>
+        <v>6266.653908676292</v>
       </c>
       <c r="C5" t="n">
         <v>1831.226876410785</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5074.254542595254</v>
+        <v>5074.254542595252</v>
       </c>
       <c r="C6" t="n">
         <v>5792.631280138497</v>
@@ -2925,7 +2925,7 @@
         <v>23353.82600566547</v>
       </c>
       <c r="N6" t="n">
-        <v>40410.71252213967</v>
+        <v>40410.71252213961</v>
       </c>
       <c r="O6" t="n">
         <v>65853.40453576544</v>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5289.089288037956</v>
+        <v>5289.089288037959</v>
       </c>
       <c r="C7" t="n">
         <v>4158.025270291973</v>
@@ -3004,7 +3004,7 @@
         <v>32653.40434540355</v>
       </c>
       <c r="N7" t="n">
-        <v>37142.13120315568</v>
+        <v>37142.1312031557</v>
       </c>
       <c r="O7" t="n">
         <v>51558.42293123015</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4672.109890061425</v>
+        <v>4672.10989006143</v>
       </c>
       <c r="C8" t="n">
         <v>4399.903137144229</v>
@@ -3065,7 +3065,7 @@
         <v>10101.21626340115</v>
       </c>
       <c r="H8" t="n">
-        <v>59146.86969847992</v>
+        <v>59146.86969847989</v>
       </c>
       <c r="I8" t="n">
         <v>60170.54196372722</v>
@@ -3083,7 +3083,7 @@
         <v>93113.03771200766</v>
       </c>
       <c r="N8" t="n">
-        <v>54626.80884709458</v>
+        <v>54626.80884709453</v>
       </c>
       <c r="O8" t="n">
         <v>58890.66862688808</v>
@@ -3101,7 +3101,7 @@
         <v>138600.7316253199</v>
       </c>
       <c r="T8" t="n">
-        <v>3144.517245499744</v>
+        <v>3144.517245499742</v>
       </c>
       <c r="U8" t="n">
         <v>2161.05808851749</v>
@@ -3144,7 +3144,7 @@
         <v>10170.7379771578</v>
       </c>
       <c r="H9" t="n">
-        <v>93099.53542619559</v>
+        <v>93099.53542619558</v>
       </c>
       <c r="I9" t="n">
         <v>103784.7409000245</v>
@@ -3180,7 +3180,7 @@
         <v>183037.9217082855</v>
       </c>
       <c r="T9" t="n">
-        <v>5781.04437568983</v>
+        <v>5781.044375689828</v>
       </c>
       <c r="U9" t="n">
         <v>3432.693882332068</v>
@@ -3223,7 +3223,7 @@
         <v>14501.97652046093</v>
       </c>
       <c r="H10" t="n">
-        <v>89206.19317416742</v>
+        <v>89206.19317416743</v>
       </c>
       <c r="I10" t="n">
         <v>78734.62914584074</v>
@@ -3259,7 +3259,7 @@
         <v>191392.0030249272</v>
       </c>
       <c r="T10" t="n">
-        <v>7269.156354257552</v>
+        <v>7269.156354257551</v>
       </c>
       <c r="U10" t="n">
         <v>6587.915076640498</v>
@@ -3417,7 +3417,7 @@
         <v>251295.4843198789</v>
       </c>
       <c r="T12" t="n">
-        <v>7284.490390018426</v>
+        <v>7284.490390018425</v>
       </c>
       <c r="U12" t="n">
         <v>4515.510605279186</v>
@@ -3637,7 +3637,7 @@
         <v>16.65541692317058</v>
       </c>
       <c r="T2" t="n">
-        <v>7.800822651136839</v>
+        <v>7.800822651136845</v>
       </c>
       <c r="U2" t="n">
         <v>4.163945805721553</v>
@@ -3698,7 +3698,7 @@
         <v>27.34697993133182</v>
       </c>
       <c r="N3" t="n">
-        <v>7.18663271934372</v>
+        <v>7.186632719343724</v>
       </c>
       <c r="O3" t="n">
         <v>12.6963764669278</v>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.345265714000422</v>
+        <v>5.345265714000427</v>
       </c>
       <c r="C4" t="n">
         <v>3.61971983471546</v>
@@ -3777,7 +3777,7 @@
         <v>41.47238070599524</v>
       </c>
       <c r="N4" t="n">
-        <v>9.911764235633045</v>
+        <v>9.911764235633054</v>
       </c>
       <c r="O4" t="n">
         <v>5.952073234211847</v>
@@ -3795,7 +3795,7 @@
         <v>21.72727969864855</v>
       </c>
       <c r="T4" t="n">
-        <v>9.991154849942557</v>
+        <v>9.991154849942552</v>
       </c>
       <c r="U4" t="n">
         <v>7.983261306523818</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.12997670376767</v>
+        <v>11.12997670376768</v>
       </c>
       <c r="C5" t="n">
         <v>3.364917480840423</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.715084656748189</v>
+        <v>9.715084656748186</v>
       </c>
       <c r="C6" t="n">
         <v>10.20303101822702</v>
@@ -3935,7 +3935,7 @@
         <v>7.162204211097505</v>
       </c>
       <c r="N6" t="n">
-        <v>6.855005696756399</v>
+        <v>6.855005696756391</v>
       </c>
       <c r="O6" t="n">
         <v>12.34262583221478</v>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.573196339785166</v>
+        <v>9.573196339785179</v>
       </c>
       <c r="C7" t="n">
         <v>8.574333616813329</v>
@@ -4014,7 +4014,7 @@
         <v>11.31530867562364</v>
       </c>
       <c r="N7" t="n">
-        <v>6.6767650761424</v>
+        <v>6.676765076142405</v>
       </c>
       <c r="O7" t="n">
         <v>8.409128756017719</v>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.859180198537908</v>
+        <v>6.859180198537913</v>
       </c>
       <c r="C8" t="n">
         <v>7.413656742670789</v>
@@ -4075,7 +4075,7 @@
         <v>16.78120305942506</v>
       </c>
       <c r="H8" t="n">
-        <v>11.33716187820806</v>
+        <v>11.33716187820805</v>
       </c>
       <c r="I8" t="n">
         <v>9.591498048199464</v>
@@ -4093,7 +4093,7 @@
         <v>19.58476580228633</v>
       </c>
       <c r="N8" t="n">
-        <v>9.786751488956265</v>
+        <v>9.786751488956257</v>
       </c>
       <c r="O8" t="n">
         <v>9.735149338341314</v>
@@ -4111,7 +4111,7 @@
         <v>24.03597018976452</v>
       </c>
       <c r="T8" t="n">
-        <v>8.414887820570312</v>
+        <v>8.414887820570309</v>
       </c>
       <c r="U8" t="n">
         <v>6.168853038880812</v>
@@ -4154,7 +4154,7 @@
         <v>15.71534652862777</v>
       </c>
       <c r="H9" t="n">
-        <v>19.02816671285936</v>
+        <v>19.02816671285935</v>
       </c>
       <c r="I9" t="n">
         <v>21.30058227596863</v>
@@ -4233,7 +4233,7 @@
         <v>35.12513849754712</v>
       </c>
       <c r="H10" t="n">
-        <v>20.44162596226063</v>
+        <v>20.44162596226064</v>
       </c>
       <c r="I10" t="n">
         <v>15.50124186398994</v>
@@ -4269,7 +4269,7 @@
         <v>48.6502884410807</v>
       </c>
       <c r="T10" t="n">
-        <v>32.24449418779277</v>
+        <v>32.24449418779276</v>
       </c>
       <c r="U10" t="n">
         <v>31.02885054739412</v>
@@ -4312,7 +4312,7 @@
         <v>77.31089133281878</v>
       </c>
       <c r="H11" t="n">
-        <v>38.88713772582025</v>
+        <v>38.88713772582026</v>
       </c>
       <c r="I11" t="n">
         <v>33.46364262822199</v>
@@ -4427,7 +4427,7 @@
         <v>146.2114039732248</v>
       </c>
       <c r="T12" t="n">
-        <v>58.89521625563781</v>
+        <v>58.89521625563779</v>
       </c>
       <c r="U12" t="n">
         <v>35.93272438798667</v>

--- a/wfcv_errors.xlsx
+++ b/wfcv_errors.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,7 +571,7 @@
         <v>13707.66666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>72184.56343936158</v>
+        <v>72184.56343936159</v>
       </c>
       <c r="I2" t="n">
         <v>82854.29427083333</v>
@@ -747,7 +747,7 @@
         <v>124410.610197756</v>
       </c>
       <c r="N4" t="n">
-        <v>51237.71816595438</v>
+        <v>51237.71816595436</v>
       </c>
       <c r="O4" t="n">
         <v>31007.625</v>
@@ -765,7 +765,7 @@
         <v>109694.893124569</v>
       </c>
       <c r="T4" t="n">
-        <v>2501.413806156802</v>
+        <v>2501.413806156803</v>
       </c>
       <c r="U4" t="n">
         <v>2046.853515625</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4903.130554260567</v>
+        <v>4903.130554260562</v>
       </c>
       <c r="C5" t="n">
         <v>1506.654947916667</v>
@@ -844,7 +844,7 @@
         <v>73429.84124377758</v>
       </c>
       <c r="T5" t="n">
-        <v>2035.242894637773</v>
+        <v>2035.242894637774</v>
       </c>
       <c r="U5" t="n">
         <v>1495.989583333333</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4364.963870032741</v>
+        <v>4364.963870032744</v>
       </c>
       <c r="C6" t="n">
         <v>4696.81640625</v>
@@ -905,7 +905,7 @@
         <v>18991.37853657941</v>
       </c>
       <c r="N6" t="n">
-        <v>36046.26910584783</v>
+        <v>36046.26910584787</v>
       </c>
       <c r="O6" t="n">
         <v>64902.41666666666</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4241.459117188369</v>
+        <v>4241.459117188359</v>
       </c>
       <c r="C7" t="n">
         <v>3895.307291666667</v>
@@ -984,7 +984,7 @@
         <v>30311.20154526455</v>
       </c>
       <c r="N7" t="n">
-        <v>35751.69722979813</v>
+        <v>35751.6972297981</v>
       </c>
       <c r="O7" t="n">
         <v>44879.83333333334</v>
@@ -1045,7 +1045,7 @@
         <v>9010.666666666666</v>
       </c>
       <c r="H8" t="n">
-        <v>43006.69727450332</v>
+        <v>43006.69727450333</v>
       </c>
       <c r="I8" t="n">
         <v>38301.96875</v>
@@ -1063,7 +1063,7 @@
         <v>73236.62464174563</v>
       </c>
       <c r="N8" t="n">
-        <v>53527.76611976925</v>
+        <v>53527.76611976929</v>
       </c>
       <c r="O8" t="n">
         <v>53437.63541666666</v>
@@ -1081,7 +1081,7 @@
         <v>131160.5307251292</v>
       </c>
       <c r="T8" t="n">
-        <v>2517.690965668587</v>
+        <v>2517.690965668588</v>
       </c>
       <c r="U8" t="n">
         <v>1749.504557291667</v>
@@ -1160,7 +1160,7 @@
         <v>179783.4296532094</v>
       </c>
       <c r="T9" t="n">
-        <v>4672.590531783036</v>
+        <v>4672.590531783037</v>
       </c>
       <c r="U9" t="n">
         <v>2930.623697916667</v>
@@ -1176,243 +1176,6 @@
       </c>
       <c r="Y9" t="n">
         <v>8703.92228251391</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>H9</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>12625.28378144078</v>
-      </c>
-      <c r="C10" t="n">
-        <v>8884.592447916666</v>
-      </c>
-      <c r="D10" t="n">
-        <v>14205.41586624551</v>
-      </c>
-      <c r="E10" t="n">
-        <v>10843.15659199261</v>
-      </c>
-      <c r="F10" t="n">
-        <v>209788.1215705172</v>
-      </c>
-      <c r="G10" t="n">
-        <v>13235</v>
-      </c>
-      <c r="H10" t="n">
-        <v>80597.60424170281</v>
-      </c>
-      <c r="I10" t="n">
-        <v>65357.1875</v>
-      </c>
-      <c r="J10" t="n">
-        <v>96433.68371481383</v>
-      </c>
-      <c r="K10" t="n">
-        <v>64840.72240243596</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1421707.365679952</v>
-      </c>
-      <c r="M10" t="n">
-        <v>102523.289456092</v>
-      </c>
-      <c r="N10" t="n">
-        <v>97710.31683253801</v>
-      </c>
-      <c r="O10" t="n">
-        <v>88231.36458333333</v>
-      </c>
-      <c r="P10" t="n">
-        <v>78111.55878251062</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>97369.71417968359</v>
-      </c>
-      <c r="R10" t="n">
-        <v>507482.7967964285</v>
-      </c>
-      <c r="S10" t="n">
-        <v>188461.891614156</v>
-      </c>
-      <c r="T10" t="n">
-        <v>7101.126866522368</v>
-      </c>
-      <c r="U10" t="n">
-        <v>6031.252604166667</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4371.312945010436</v>
-      </c>
-      <c r="W10" t="n">
-        <v>6060.106333717648</v>
-      </c>
-      <c r="X10" t="n">
-        <v>112359.6135028956</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>9804.345708220673</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>H10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>16930.15222450698</v>
-      </c>
-      <c r="C11" t="n">
-        <v>20172.94661458333</v>
-      </c>
-      <c r="D11" t="n">
-        <v>17605.31195674774</v>
-      </c>
-      <c r="E11" t="n">
-        <v>15077.79640533145</v>
-      </c>
-      <c r="F11" t="n">
-        <v>461592.454487648</v>
-      </c>
-      <c r="G11" t="n">
-        <v>21409</v>
-      </c>
-      <c r="H11" t="n">
-        <v>104945.0940895262</v>
-      </c>
-      <c r="I11" t="n">
-        <v>88535.5625</v>
-      </c>
-      <c r="J11" t="n">
-        <v>56639.84458176976</v>
-      </c>
-      <c r="K11" t="n">
-        <v>58813.07584177571</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2764385.460942686</v>
-      </c>
-      <c r="M11" t="n">
-        <v>118900.516538205</v>
-      </c>
-      <c r="N11" t="n">
-        <v>149120.9369619409</v>
-      </c>
-      <c r="O11" t="n">
-        <v>115142.3020833333</v>
-      </c>
-      <c r="P11" t="n">
-        <v>80799.97256832389</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>136338.1607174093</v>
-      </c>
-      <c r="R11" t="n">
-        <v>769076.6150977624</v>
-      </c>
-      <c r="S11" t="n">
-        <v>209996.8644067796</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7101.441502044247</v>
-      </c>
-      <c r="U11" t="n">
-        <v>8047.544270833333</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2812.466998506448</v>
-      </c>
-      <c r="W11" t="n">
-        <v>4725.741493766734</v>
-      </c>
-      <c r="X11" t="n">
-        <v>261476.9050057846</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>7791.389585307269</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>H11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>30045.9692099567</v>
-      </c>
-      <c r="C12" t="n">
-        <v>33288.51302083334</v>
-      </c>
-      <c r="D12" t="n">
-        <v>28684.95923563236</v>
-      </c>
-      <c r="E12" t="n">
-        <v>27201.05017416922</v>
-      </c>
-      <c r="F12" t="n">
-        <v>741193.3133847368</v>
-      </c>
-      <c r="G12" t="n">
-        <v>38913</v>
-      </c>
-      <c r="H12" t="n">
-        <v>166989.5451345228</v>
-      </c>
-      <c r="I12" t="n">
-        <v>127420.0833333333</v>
-      </c>
-      <c r="J12" t="n">
-        <v>98634.54060048012</v>
-      </c>
-      <c r="K12" t="n">
-        <v>106125.3487399855</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3586594.831203761</v>
-      </c>
-      <c r="M12" t="n">
-        <v>239328.7548444103</v>
-      </c>
-      <c r="N12" t="n">
-        <v>198056.0800787407</v>
-      </c>
-      <c r="O12" t="n">
-        <v>165441.53125</v>
-      </c>
-      <c r="P12" t="n">
-        <v>96272.77189015299</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>189378.8568428295</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1670574.647135337</v>
-      </c>
-      <c r="S12" t="n">
-        <v>250038.5833333333</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6799.315943783065</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4225.175130208333</v>
-      </c>
-      <c r="V12" t="n">
-        <v>3671.890866043124</v>
-      </c>
-      <c r="W12" t="n">
-        <v>5721.086488161414</v>
-      </c>
-      <c r="X12" t="n">
-        <v>405487.3094936037</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>11306.33083068272</v>
       </c>
     </row>
   </sheetData>
@@ -1426,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1757,7 +1520,7 @@
         <v>16149525145.71921</v>
       </c>
       <c r="N4" t="n">
-        <v>3444492794.655293</v>
+        <v>3444492794.65529</v>
       </c>
       <c r="O4" t="n">
         <v>2127819744.307292</v>
@@ -1775,7 +1538,7 @@
         <v>12107428246.84086</v>
       </c>
       <c r="T4" t="n">
-        <v>8796029.302870719</v>
+        <v>8796029.302870721</v>
       </c>
       <c r="U4" t="n">
         <v>9016670.528036753</v>
@@ -1800,7 +1563,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39270951.21112785</v>
+        <v>39270951.21112776</v>
       </c>
       <c r="C5" t="n">
         <v>3353391.872889201</v>
@@ -1879,7 +1642,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25748059.16304855</v>
+        <v>25748059.16304857</v>
       </c>
       <c r="C6" t="n">
         <v>33554577.14763895</v>
@@ -1915,7 +1678,7 @@
         <v>545401189.1028966</v>
       </c>
       <c r="N6" t="n">
-        <v>1633025686.547011</v>
+        <v>1633025686.547016</v>
       </c>
       <c r="O6" t="n">
         <v>4336670888.951172</v>
@@ -1958,7 +1721,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27974465.49683788</v>
+        <v>27974465.49683777</v>
       </c>
       <c r="C7" t="n">
         <v>17289174.14838664</v>
@@ -1994,7 +1757,7 @@
         <v>1066244815.344419</v>
       </c>
       <c r="N7" t="n">
-        <v>1379537910.312433</v>
+        <v>1379537910.312431</v>
       </c>
       <c r="O7" t="n">
         <v>2658270975.155599</v>
@@ -2055,7 +1818,7 @@
         <v>102034570</v>
       </c>
       <c r="H8" t="n">
-        <v>3498352195.128958</v>
+        <v>3498352195.128962</v>
       </c>
       <c r="I8" t="n">
         <v>3620494120.208659</v>
@@ -2073,7 +1836,7 @@
         <v>8670037791.957762</v>
       </c>
       <c r="N8" t="n">
-        <v>2984088244.817005</v>
+        <v>2984088244.81701</v>
       </c>
       <c r="O8" t="n">
         <v>3468110851.32194</v>
@@ -2091,7 +1854,7 @@
         <v>19210162807.07394</v>
       </c>
       <c r="T8" t="n">
-        <v>9887988.707245287</v>
+        <v>9887988.7072453</v>
       </c>
       <c r="U8" t="n">
         <v>4670172.061946869</v>
@@ -2170,7 +1933,7 @@
         <v>33502880783.28843</v>
       </c>
       <c r="T9" t="n">
-        <v>33420474.073695</v>
+        <v>33420474.07369502</v>
       </c>
       <c r="U9" t="n">
         <v>11783387.28980001</v>
@@ -2186,243 +1949,6 @@
       </c>
       <c r="Y9" t="n">
         <v>103847019.2706245</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>H9</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>175647580.5315764</v>
-      </c>
-      <c r="C10" t="n">
-        <v>90376370.59467061</v>
-      </c>
-      <c r="D10" t="n">
-        <v>213820349.4378951</v>
-      </c>
-      <c r="E10" t="n">
-        <v>146923458.4059441</v>
-      </c>
-      <c r="F10" t="n">
-        <v>117199435837.548</v>
-      </c>
-      <c r="G10" t="n">
-        <v>210307323</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7957744900.626878</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6199141826.733073</v>
-      </c>
-      <c r="J10" t="n">
-        <v>11164814243.38097</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4336149033.751409</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5191776377339.425</v>
-      </c>
-      <c r="M10" t="n">
-        <v>11372805096.2049</v>
-      </c>
-      <c r="N10" t="n">
-        <v>10386892305.29515</v>
-      </c>
-      <c r="O10" t="n">
-        <v>9029090399.948893</v>
-      </c>
-      <c r="P10" t="n">
-        <v>7462015146.989143</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>10428908768.45368</v>
-      </c>
-      <c r="R10" t="n">
-        <v>596510040468.7063</v>
-      </c>
-      <c r="S10" t="n">
-        <v>36630898821.89375</v>
-      </c>
-      <c r="T10" t="n">
-        <v>52840634.10264293</v>
-      </c>
-      <c r="U10" t="n">
-        <v>43400625.05702718</v>
-      </c>
-      <c r="V10" t="n">
-        <v>23011413.67906871</v>
-      </c>
-      <c r="W10" t="n">
-        <v>42759012.79789517</v>
-      </c>
-      <c r="X10" t="n">
-        <v>35325980536.64599</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>106659743.1822421</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>H10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>372630597.8047811</v>
-      </c>
-      <c r="C11" t="n">
-        <v>606406777.9172617</v>
-      </c>
-      <c r="D11" t="n">
-        <v>364843362.8226473</v>
-      </c>
-      <c r="E11" t="n">
-        <v>317448292.3816548</v>
-      </c>
-      <c r="F11" t="n">
-        <v>325272176521.1472</v>
-      </c>
-      <c r="G11" t="n">
-        <v>635187753</v>
-      </c>
-      <c r="H11" t="n">
-        <v>11691006795.8308</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8970982479.430338</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3381395533.961497</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3474125579.106647</v>
-      </c>
-      <c r="L11" t="n">
-        <v>11579812330066.04</v>
-      </c>
-      <c r="M11" t="n">
-        <v>15342029845.0944</v>
-      </c>
-      <c r="N11" t="n">
-        <v>27077784588.4658</v>
-      </c>
-      <c r="O11" t="n">
-        <v>13892577130.80762</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8727998729.923687</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>19163072414.63404</v>
-      </c>
-      <c r="R11" t="n">
-        <v>965574514892.479</v>
-      </c>
-      <c r="S11" t="n">
-        <v>45002332481.52705</v>
-      </c>
-      <c r="T11" t="n">
-        <v>54749608.22585229</v>
-      </c>
-      <c r="U11" t="n">
-        <v>75279716.0410258</v>
-      </c>
-      <c r="V11" t="n">
-        <v>10312893.4181177</v>
-      </c>
-      <c r="W11" t="n">
-        <v>28875322.11744221</v>
-      </c>
-      <c r="X11" t="n">
-        <v>104306517017.2542</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>64061503.57772753</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>H11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>922589630.0857261</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1130583621.496643</v>
-      </c>
-      <c r="D12" t="n">
-        <v>913007011.8065654</v>
-      </c>
-      <c r="E12" t="n">
-        <v>858185295.404788</v>
-      </c>
-      <c r="F12" t="n">
-        <v>567633990513.5776</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1575327651</v>
-      </c>
-      <c r="H12" t="n">
-        <v>30560451325.96666</v>
-      </c>
-      <c r="I12" t="n">
-        <v>20167926607.62239</v>
-      </c>
-      <c r="J12" t="n">
-        <v>11380706589.21525</v>
-      </c>
-      <c r="K12" t="n">
-        <v>15588206261.01287</v>
-      </c>
-      <c r="L12" t="n">
-        <v>13223070788585.14</v>
-      </c>
-      <c r="M12" t="n">
-        <v>61895444363.27143</v>
-      </c>
-      <c r="N12" t="n">
-        <v>41702935529.07891</v>
-      </c>
-      <c r="O12" t="n">
-        <v>28212818044.71777</v>
-      </c>
-      <c r="P12" t="n">
-        <v>14990236986.25175</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>37519153060.88023</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3547974876823.054</v>
-      </c>
-      <c r="S12" t="n">
-        <v>63149420439.56248</v>
-      </c>
-      <c r="T12" t="n">
-        <v>53063800.24227079</v>
-      </c>
-      <c r="U12" t="n">
-        <v>20389836.02638881</v>
-      </c>
-      <c r="V12" t="n">
-        <v>16942307.19701349</v>
-      </c>
-      <c r="W12" t="n">
-        <v>39180611.36930978</v>
-      </c>
-      <c r="X12" t="n">
-        <v>167044750326.2195</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>133548763.8659393</v>
       </c>
     </row>
   </sheetData>
@@ -2436,7 +1962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2767,7 +2293,7 @@
         <v>127080.7819684755</v>
       </c>
       <c r="N4" t="n">
-        <v>58689.80145353444</v>
+        <v>58689.80145353441</v>
       </c>
       <c r="O4" t="n">
         <v>46128.29656845451</v>
@@ -2810,7 +2336,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6266.653908676292</v>
+        <v>6266.653908676285</v>
       </c>
       <c r="C5" t="n">
         <v>1831.226876410785</v>
@@ -2889,7 +2415,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5074.254542595252</v>
+        <v>5074.254542595254</v>
       </c>
       <c r="C6" t="n">
         <v>5792.631280138497</v>
@@ -2925,7 +2451,7 @@
         <v>23353.82600566547</v>
       </c>
       <c r="N6" t="n">
-        <v>40410.71252213961</v>
+        <v>40410.71252213967</v>
       </c>
       <c r="O6" t="n">
         <v>65853.40453576544</v>
@@ -2968,7 +2494,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5289.089288037959</v>
+        <v>5289.089288037948</v>
       </c>
       <c r="C7" t="n">
         <v>4158.025270291973</v>
@@ -3004,7 +2530,7 @@
         <v>32653.40434540355</v>
       </c>
       <c r="N7" t="n">
-        <v>37142.1312031557</v>
+        <v>37142.13120315568</v>
       </c>
       <c r="O7" t="n">
         <v>51558.42293123015</v>
@@ -3065,7 +2591,7 @@
         <v>10101.21626340115</v>
       </c>
       <c r="H8" t="n">
-        <v>59146.86969847989</v>
+        <v>59146.86969847992</v>
       </c>
       <c r="I8" t="n">
         <v>60170.54196372722</v>
@@ -3083,7 +2609,7 @@
         <v>93113.03771200766</v>
       </c>
       <c r="N8" t="n">
-        <v>54626.80884709453</v>
+        <v>54626.80884709458</v>
       </c>
       <c r="O8" t="n">
         <v>58890.66862688808</v>
@@ -3101,7 +2627,7 @@
         <v>138600.7316253199</v>
       </c>
       <c r="T8" t="n">
-        <v>3144.517245499742</v>
+        <v>3144.517245499744</v>
       </c>
       <c r="U8" t="n">
         <v>2161.05808851749</v>
@@ -3180,7 +2706,7 @@
         <v>183037.9217082855</v>
       </c>
       <c r="T9" t="n">
-        <v>5781.044375689828</v>
+        <v>5781.04437568983</v>
       </c>
       <c r="U9" t="n">
         <v>3432.693882332068</v>
@@ -3196,243 +2722,6 @@
       </c>
       <c r="Y9" t="n">
         <v>10190.53576955719</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>H9</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>13253.21019721548</v>
-      </c>
-      <c r="C10" t="n">
-        <v>9506.648757299841</v>
-      </c>
-      <c r="D10" t="n">
-        <v>14622.59721930051</v>
-      </c>
-      <c r="E10" t="n">
-        <v>12121.19871984385</v>
-      </c>
-      <c r="F10" t="n">
-        <v>342344.0314034232</v>
-      </c>
-      <c r="G10" t="n">
-        <v>14501.97652046093</v>
-      </c>
-      <c r="H10" t="n">
-        <v>89206.19317416743</v>
-      </c>
-      <c r="I10" t="n">
-        <v>78734.62914584074</v>
-      </c>
-      <c r="J10" t="n">
-        <v>105663.6846006279</v>
-      </c>
-      <c r="K10" t="n">
-        <v>65849.44216735179</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2278546.988178963</v>
-      </c>
-      <c r="M10" t="n">
-        <v>106643.3546743767</v>
-      </c>
-      <c r="N10" t="n">
-        <v>101916.1042490104</v>
-      </c>
-      <c r="O10" t="n">
-        <v>95021.52598200522</v>
-      </c>
-      <c r="P10" t="n">
-        <v>86382.95634550338</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>102122.028810897</v>
-      </c>
-      <c r="R10" t="n">
-        <v>772340.6246396122</v>
-      </c>
-      <c r="S10" t="n">
-        <v>191392.0030249272</v>
-      </c>
-      <c r="T10" t="n">
-        <v>7269.156354257551</v>
-      </c>
-      <c r="U10" t="n">
-        <v>6587.915076640498</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4797.021334022678</v>
-      </c>
-      <c r="W10" t="n">
-        <v>6539.037604869326</v>
-      </c>
-      <c r="X10" t="n">
-        <v>187952.0697854801</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>10327.62040269888</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>H10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>19303.64208652816</v>
-      </c>
-      <c r="C11" t="n">
-        <v>24625.32797583134</v>
-      </c>
-      <c r="D11" t="n">
-        <v>19100.87335235348</v>
-      </c>
-      <c r="E11" t="n">
-        <v>17817.07867136627</v>
-      </c>
-      <c r="F11" t="n">
-        <v>570326.3771921715</v>
-      </c>
-      <c r="G11" t="n">
-        <v>25202.93143664046</v>
-      </c>
-      <c r="H11" t="n">
-        <v>108124.9591714642</v>
-      </c>
-      <c r="I11" t="n">
-        <v>94715.27057148883</v>
-      </c>
-      <c r="J11" t="n">
-        <v>58149.76813334251</v>
-      </c>
-      <c r="K11" t="n">
-        <v>58941.71340491085</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3402912.330646507</v>
-      </c>
-      <c r="M11" t="n">
-        <v>123862.9478298268</v>
-      </c>
-      <c r="N11" t="n">
-        <v>164553.2879904434</v>
-      </c>
-      <c r="O11" t="n">
-        <v>117866.7770442868</v>
-      </c>
-      <c r="P11" t="n">
-        <v>93423.75891561892</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>138430.7495270977</v>
-      </c>
-      <c r="R11" t="n">
-        <v>982636.5120900398</v>
-      </c>
-      <c r="S11" t="n">
-        <v>212137.531996408</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7399.297819783462</v>
-      </c>
-      <c r="U11" t="n">
-        <v>8676.388421516513</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3211.369399199927</v>
-      </c>
-      <c r="W11" t="n">
-        <v>5373.576287486966</v>
-      </c>
-      <c r="X11" t="n">
-        <v>322965.1947458954</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>8003.843050543129</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>H11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>30374.16056594365</v>
-      </c>
-      <c r="C12" t="n">
-        <v>33624.15235357827</v>
-      </c>
-      <c r="D12" t="n">
-        <v>30216.00588771728</v>
-      </c>
-      <c r="E12" t="n">
-        <v>29294.79980141165</v>
-      </c>
-      <c r="F12" t="n">
-        <v>753414.8860445868</v>
-      </c>
-      <c r="G12" t="n">
-        <v>39690.39746588588</v>
-      </c>
-      <c r="H12" t="n">
-        <v>174815.4779359272</v>
-      </c>
-      <c r="I12" t="n">
-        <v>142013.8254101424</v>
-      </c>
-      <c r="J12" t="n">
-        <v>106680.3945868933</v>
-      </c>
-      <c r="K12" t="n">
-        <v>124852.7383000184</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3636354.051599644</v>
-      </c>
-      <c r="M12" t="n">
-        <v>248787.9505990421</v>
-      </c>
-      <c r="N12" t="n">
-        <v>204212.9661140029</v>
-      </c>
-      <c r="O12" t="n">
-        <v>167966.7170742995</v>
-      </c>
-      <c r="P12" t="n">
-        <v>122434.6233148603</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>193698.6139880206</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1883606.879585827</v>
-      </c>
-      <c r="S12" t="n">
-        <v>251295.4843198789</v>
-      </c>
-      <c r="T12" t="n">
-        <v>7284.490390018425</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4515.510605279186</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4116.103399698979</v>
-      </c>
-      <c r="W12" t="n">
-        <v>6259.441777771383</v>
-      </c>
-      <c r="X12" t="n">
-        <v>408711.0841734287</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>11556.33003448496</v>
       </c>
     </row>
   </sheetData>
@@ -3446,7 +2735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3777,7 +3066,7 @@
         <v>41.47238070599524</v>
       </c>
       <c r="N4" t="n">
-        <v>9.911764235633054</v>
+        <v>9.911764235633051</v>
       </c>
       <c r="O4" t="n">
         <v>5.952073234211847</v>
@@ -3795,7 +3084,7 @@
         <v>21.72727969864855</v>
       </c>
       <c r="T4" t="n">
-        <v>9.991154849942552</v>
+        <v>9.991154849942557</v>
       </c>
       <c r="U4" t="n">
         <v>7.983261306523818</v>
@@ -3820,7 +3109,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.12997670376768</v>
+        <v>11.12997670376767</v>
       </c>
       <c r="C5" t="n">
         <v>3.364917480840423</v>
@@ -3874,7 +3163,7 @@
         <v>14.22701261769216</v>
       </c>
       <c r="T5" t="n">
-        <v>7.582224630696717</v>
+        <v>7.582224630696722</v>
       </c>
       <c r="U5" t="n">
         <v>5.700110104086486</v>
@@ -3899,7 +3188,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.715084656748186</v>
+        <v>9.715084656748189</v>
       </c>
       <c r="C6" t="n">
         <v>10.20303101822702</v>
@@ -3935,7 +3224,7 @@
         <v>7.162204211097505</v>
       </c>
       <c r="N6" t="n">
-        <v>6.855005696756391</v>
+        <v>6.855005696756399</v>
       </c>
       <c r="O6" t="n">
         <v>12.34262583221478</v>
@@ -3978,7 +3267,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.573196339785179</v>
+        <v>9.573196339785156</v>
       </c>
       <c r="C7" t="n">
         <v>8.574333616813329</v>
@@ -4014,7 +3303,7 @@
         <v>11.31530867562364</v>
       </c>
       <c r="N7" t="n">
-        <v>6.676765076142405</v>
+        <v>6.6767650761424</v>
       </c>
       <c r="O7" t="n">
         <v>8.409128756017719</v>
@@ -4075,7 +3364,7 @@
         <v>16.78120305942506</v>
       </c>
       <c r="H8" t="n">
-        <v>11.33716187820805</v>
+        <v>11.33716187820806</v>
       </c>
       <c r="I8" t="n">
         <v>9.591498048199464</v>
@@ -4093,7 +3382,7 @@
         <v>19.58476580228633</v>
       </c>
       <c r="N8" t="n">
-        <v>9.786751488956257</v>
+        <v>9.786751488956265</v>
       </c>
       <c r="O8" t="n">
         <v>9.735149338341314</v>
@@ -4111,7 +3400,7 @@
         <v>24.03597018976452</v>
       </c>
       <c r="T8" t="n">
-        <v>8.414887820570309</v>
+        <v>8.414887820570312</v>
       </c>
       <c r="U8" t="n">
         <v>6.168853038880812</v>
@@ -4206,243 +3495,6 @@
       </c>
       <c r="Y9" t="n">
         <v>26.68867374117026</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>H9</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>32.09257365449764</v>
-      </c>
-      <c r="C10" t="n">
-        <v>22.68441234299554</v>
-      </c>
-      <c r="D10" t="n">
-        <v>35.19096043630014</v>
-      </c>
-      <c r="E10" t="n">
-        <v>20.19672986718173</v>
-      </c>
-      <c r="F10" t="n">
-        <v>707.946786377546</v>
-      </c>
-      <c r="G10" t="n">
-        <v>35.12513849754712</v>
-      </c>
-      <c r="H10" t="n">
-        <v>20.44162596226064</v>
-      </c>
-      <c r="I10" t="n">
-        <v>15.50124186398994</v>
-      </c>
-      <c r="J10" t="n">
-        <v>24.69399604008278</v>
-      </c>
-      <c r="K10" t="n">
-        <v>18.29922517489014</v>
-      </c>
-      <c r="L10" t="n">
-        <v>565.2599741731888</v>
-      </c>
-      <c r="M10" t="n">
-        <v>27.67412076011604</v>
-      </c>
-      <c r="N10" t="n">
-        <v>31.59913271317306</v>
-      </c>
-      <c r="O10" t="n">
-        <v>29.22249417649837</v>
-      </c>
-      <c r="P10" t="n">
-        <v>16.4793000733312</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>30.57816075759419</v>
-      </c>
-      <c r="R10" t="n">
-        <v>228.3620560060585</v>
-      </c>
-      <c r="S10" t="n">
-        <v>48.6502884410807</v>
-      </c>
-      <c r="T10" t="n">
-        <v>32.24449418779276</v>
-      </c>
-      <c r="U10" t="n">
-        <v>31.02885054739412</v>
-      </c>
-      <c r="V10" t="n">
-        <v>15.81998582037875</v>
-      </c>
-      <c r="W10" t="n">
-        <v>23.64014478017123</v>
-      </c>
-      <c r="X10" t="n">
-        <v>791.6047463376083</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>38.08864318487765</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>H10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>59.65596970526536</v>
-      </c>
-      <c r="C11" t="n">
-        <v>74.18064234496207</v>
-      </c>
-      <c r="D11" t="n">
-        <v>59.88814978922026</v>
-      </c>
-      <c r="E11" t="n">
-        <v>54.58596065801887</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1711.987210858065</v>
-      </c>
-      <c r="G11" t="n">
-        <v>77.31089133281878</v>
-      </c>
-      <c r="H11" t="n">
-        <v>38.88713772582026</v>
-      </c>
-      <c r="I11" t="n">
-        <v>33.46364262822199</v>
-      </c>
-      <c r="J11" t="n">
-        <v>20.58264489373508</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20.68665990310879</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1129.795433205618</v>
-      </c>
-      <c r="M11" t="n">
-        <v>44.52788225952673</v>
-      </c>
-      <c r="N11" t="n">
-        <v>69.05529141383447</v>
-      </c>
-      <c r="O11" t="n">
-        <v>50.21502320963754</v>
-      </c>
-      <c r="P11" t="n">
-        <v>28.54993201799183</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>57.82517563202006</v>
-      </c>
-      <c r="R11" t="n">
-        <v>370.1752129496237</v>
-      </c>
-      <c r="S11" t="n">
-        <v>89.01314252601313</v>
-      </c>
-      <c r="T11" t="n">
-        <v>36.34928824899742</v>
-      </c>
-      <c r="U11" t="n">
-        <v>39.78977654229446</v>
-      </c>
-      <c r="V11" t="n">
-        <v>12.61567410377586</v>
-      </c>
-      <c r="W11" t="n">
-        <v>22.21777213232927</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1746.023120768679</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>40.69252170884064</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>H11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>177.871429502445</v>
-      </c>
-      <c r="C12" t="n">
-        <v>196.5435921355121</v>
-      </c>
-      <c r="D12" t="n">
-        <v>183.0251233418866</v>
-      </c>
-      <c r="E12" t="n">
-        <v>177.0301035088983</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4177.840880281125</v>
-      </c>
-      <c r="G12" t="n">
-        <v>235.6541031665305</v>
-      </c>
-      <c r="H12" t="n">
-        <v>115.8431003919654</v>
-      </c>
-      <c r="I12" t="n">
-        <v>92.37035338833097</v>
-      </c>
-      <c r="J12" t="n">
-        <v>71.08020360896873</v>
-      </c>
-      <c r="K12" t="n">
-        <v>82.83291796273238</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2239.876220919736</v>
-      </c>
-      <c r="M12" t="n">
-        <v>164.4551252517821</v>
-      </c>
-      <c r="N12" t="n">
-        <v>115.1021407560359</v>
-      </c>
-      <c r="O12" t="n">
-        <v>97.5134851747312</v>
-      </c>
-      <c r="P12" t="n">
-        <v>61.90866634822223</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>112.4654796872119</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1024.739484983219</v>
-      </c>
-      <c r="S12" t="n">
-        <v>146.2114039732248</v>
-      </c>
-      <c r="T12" t="n">
-        <v>58.89521625563779</v>
-      </c>
-      <c r="U12" t="n">
-        <v>35.93272438798667</v>
-      </c>
-      <c r="V12" t="n">
-        <v>32.64355458932106</v>
-      </c>
-      <c r="W12" t="n">
-        <v>50.01211659418253</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3206.877803856305</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>92.48109899280364</v>
       </c>
     </row>
   </sheetData>
